--- a/data/trans_orig/P21D5_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P21D5_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitándolo, no pudo recibir atención médica mental (psiquiatra) en 2023</t>
+          <t>Población que, necesitándolo, no pudo recibir atención médica mental (psiquiatra) en 2023 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>213889</t>
+          <t>212774</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>225750</t>
+          <t>225507</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>304958</t>
+          <t>305082</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>319021</t>
+          <t>319274</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>522709</t>
+          <t>523510</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>541787</t>
+          <t>541393</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4079</t>
+          <t>4225</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15671</t>
+          <t>16179</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11302</t>
+          <t>11303</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23439</t>
+          <t>23143</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17679</t>
+          <t>18403</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34938</t>
+          <t>34850</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2623</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>2440</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9588</t>
+          <t>9860</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2703</t>
+          <t>2847</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10093</t>
+          <t>10291</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5333</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>368</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>5423</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>703</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7563</t>
+          <t>7275</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>434254</t>
+          <t>442963</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1072918</t>
+          <t>1073032</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>872601</t>
+          <t>872081</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>899141</t>
+          <t>899237</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1184148</t>
+          <t>1123156</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1958372</t>
+          <t>1959866</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,4%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37404</t>
+          <t>37062</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>677496</t>
+          <t>673160</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30794</t>
+          <t>30125</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55620</t>
+          <t>55000</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>80506</t>
+          <t>78893</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>862137</t>
+          <t>920331</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>44,8%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>1370</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10777</t>
+          <t>11868</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2516</t>
+          <t>2479</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9763</t>
+          <t>10445</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5040</t>
+          <t>5121</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17224</t>
+          <t>16474</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>4414</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8067</t>
+          <t>7785</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8972</t>
+          <t>10226</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>271274</t>
+          <t>270580</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>293763</t>
+          <t>293173</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>287103</t>
+          <t>288492</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>304182</t>
+          <t>304282</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>566904</t>
+          <t>566366</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>594231</t>
+          <t>594347</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,48%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11519</t>
+          <t>12232</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>32259</t>
+          <t>34288</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4816</t>
+          <t>4969</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15707</t>
+          <t>16099</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>19371</t>
+          <t>18593</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>42500</t>
+          <t>45906</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13016</t>
+          <t>11486</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>683</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16866</t>
+          <t>17709</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3669</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18553</t>
+          <t>18288</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5693</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6958</t>
+          <t>7640</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>785382</t>
+          <t>834797</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1575523</t>
+          <t>1578880</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1480006</t>
+          <t>1479957</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1515362</t>
+          <t>1513314</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2188062</t>
+          <t>2162017</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3072905</t>
+          <t>3072777</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,73%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>67764</t>
+          <t>65629</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>865765</t>
+          <t>815959</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>49,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>54207</t>
+          <t>54467</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>84166</t>
+          <t>82580</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>135259</t>
+          <t>134806</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1032957</t>
+          <t>1061544</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>32,73%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>4285</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17842</t>
+          <t>18289</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>8696</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>26729</t>
+          <t>26008</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>15786</t>
+          <t>15297</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>36032</t>
+          <t>36560</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8657</t>
+          <t>9885</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2771</t>
+          <t>2867</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10979</t>
+          <t>11139</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4492</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15561</t>
+          <t>15838</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D5_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P21D5_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>220816</t>
+          <t>243287</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>212774</t>
+          <t>234767</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>225507</t>
+          <t>248515</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>312601</t>
+          <t>336023</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>305082</t>
+          <t>327612</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>319274</t>
+          <t>342951</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>533417</t>
+          <t>579310</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>523510</t>
+          <t>567529</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>541393</t>
+          <t>588097</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,55%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8533</t>
+          <t>8845</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4225</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16179</t>
+          <t>17406</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16607</t>
+          <t>18477</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11303</t>
+          <t>12270</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23143</t>
+          <t>25699</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>25140</t>
+          <t>27322</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18403</t>
+          <t>19769</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34850</t>
+          <t>38585</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>528</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>5407</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2440</t>
+          <t>2444</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9860</t>
+          <t>10852</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>5517</t>
+          <t>5935</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>2948</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10291</t>
+          <t>11709</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>995</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5392</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,22 +1099,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>388</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>5748</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2795</t>
+          <t>2893</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>802</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7275</t>
+          <t>7584</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>230877</t>
+          <t>253655</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>230877</t>
+          <t>253655</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>230877</t>
+          <t>253655</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>335993</t>
+          <t>361805</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>335993</t>
+          <t>361805</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>335993</t>
+          <t>361805</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>566870</t>
+          <t>615460</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>566870</t>
+          <t>615460</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>566870</t>
+          <t>615460</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>833475</t>
+          <t>916641</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>442963</t>
+          <t>898502</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1073032</t>
+          <t>928258</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>886275</t>
+          <t>929913</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>872081</t>
+          <t>914312</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>899237</t>
+          <t>940121</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1719750</t>
+          <t>1846554</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1123156</t>
+          <t>1827080</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1959866</t>
+          <t>1864440</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,91%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>278275</t>
+          <t>36326</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37062</t>
+          <t>25913</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>673160</t>
+          <t>53602</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>42105</t>
+          <t>45770</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30125</t>
+          <t>36672</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55000</t>
+          <t>60786</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>320381</t>
+          <t>82096</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>78893</t>
+          <t>67198</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>920331</t>
+          <t>101554</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -1520,27 +1520,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>4728</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11868</t>
+          <t>10191</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5437</t>
+          <t>5747</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>2723</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10445</t>
+          <t>11002</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>9963</t>
+          <t>10475</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16474</t>
+          <t>18203</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>660</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4414</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3496</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1660</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7785</t>
+          <t>8654</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,27 +1703,27 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>4189</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10226</t>
+          <t>9708</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1116969</t>
+          <t>958354</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1116969</t>
+          <t>958354</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1116969</t>
+          <t>958354</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>937313</t>
+          <t>985519</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>937313</t>
+          <t>985519</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>937313</t>
+          <t>985519</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2054282</t>
+          <t>1943873</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2054282</t>
+          <t>1943873</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2054282</t>
+          <t>1943873</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>283808</t>
+          <t>319987</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>270580</t>
+          <t>304698</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>293173</t>
+          <t>330185</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>298616</t>
+          <t>327343</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>288492</t>
+          <t>317180</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>304282</t>
+          <t>333201</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>582425</t>
+          <t>647330</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>566366</t>
+          <t>629107</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>594347</t>
+          <t>658229</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,47%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20066</t>
+          <t>20574</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12232</t>
+          <t>12235</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>34288</t>
+          <t>33753</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,27 +2011,27 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8786</t>
+          <t>10209</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>5686</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16099</t>
+          <t>17665</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>28852</t>
+          <t>30784</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>18593</t>
+          <t>21684</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>45906</t>
+          <t>46882</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4625</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11486</t>
+          <t>13171</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>664</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17709</t>
+          <t>12315</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>8860</t>
+          <t>8912</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>3690</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18288</t>
+          <t>19546</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>7616</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>692</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>3378</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,22 +2272,22 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2423</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>591</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7640</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>310183</t>
+          <t>347209</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>310183</t>
+          <t>347209</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>310183</t>
+          <t>347209</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>312287</t>
+          <t>342240</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>312287</t>
+          <t>342240</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>312287</t>
+          <t>342240</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>622471</t>
+          <t>689448</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>622471</t>
+          <t>689448</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>622471</t>
+          <t>689448</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1338099</t>
+          <t>1479916</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>834797</t>
+          <t>1458092</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1578880</t>
+          <t>1498658</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1497493</t>
+          <t>1593278</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1479957</t>
+          <t>1574292</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1513314</t>
+          <t>1609463</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2835592</t>
+          <t>3073194</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2162017</t>
+          <t>3044532</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3072777</t>
+          <t>3095303</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>95,28%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>306874</t>
+          <t>65745</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>65629</t>
+          <t>48847</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>815959</t>
+          <t>86722</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>67498</t>
+          <t>74456</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>54467</t>
+          <t>60809</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>82580</t>
+          <t>90815</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>374372</t>
+          <t>140201</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>134806</t>
+          <t>118990</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1061544</t>
+          <t>165949</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9676</t>
+          <t>10173</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4285</t>
+          <t>4631</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18289</t>
+          <t>18743</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14665</t>
+          <t>15150</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8696</t>
+          <t>9455</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>26008</t>
+          <t>24375</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>24340</t>
+          <t>25322</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>15297</t>
+          <t>16847</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>36560</t>
+          <t>36024</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -2771,67 +2771,67 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>993</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9885</t>
+          <t>8771</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>6679</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>3306</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>12529</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>5938</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>2867</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>11139</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>10064</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4798</t>
+          <t>5632</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15838</t>
+          <t>16318</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1658030</t>
+          <t>1559218</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1658030</t>
+          <t>1559218</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1658030</t>
+          <t>1559218</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1585593</t>
+          <t>1689563</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1585593</t>
+          <t>1689563</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1585593</t>
+          <t>1689563</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>3243623</t>
+          <t>3248781</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3243623</t>
+          <t>3248781</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3243623</t>
+          <t>3248781</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
